--- a/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 18,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 12,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 9,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,08</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,68</t>
+          <t>1,67; 15,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,45</t>
+          <t>0,0; 15,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,77</t>
+          <t>0,99; 12,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 13,58</t>
+          <t>1,56; 13,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,22</t>
+          <t>0,61; 5,99</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,43</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 12,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,24</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,06</t>
+          <t>0,51; 5,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,1</t>
+          <t>0,39; 3,86</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1697,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,01; 1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,35; 1,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,08; 0,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,59</t>
+          <t>0,49; 1,76</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4100</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3820</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5146</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4222</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1879</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>533; 4776</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2653</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6300</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2631</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>711; 8732</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2322</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2322</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2461</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>670; 5945</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2227</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>620; 6085</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3755</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3886</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3865</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3756</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4245</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>393; 4338</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3436</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4700</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>621; 5502</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>722; 7191</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2941</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2951</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3916</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2919</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3435</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1127; 7336</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4644</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10494</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>18; 6120</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0; 8558</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0; 5225</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2505; 10386</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>619; 6144</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>4279; 15396</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,32</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 12,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,01</t>
+          <t>1,68; 15,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 7,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,73</t>
+          <t>0,0; 14,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 12,15</t>
+          <t>0,95; 11,49</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,88</t>
+          <t>1,68; 14,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,99</t>
+          <t>0,62; 6,03</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,1</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,58</t>
+          <t>0,49; 5,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,2</t>
+          <t>0,47; 4,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,86</t>
+          <t>0,43; 3,81</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1842,32 +1842,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,67</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1877,22 +1877,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,44</t>
+          <t>0,35; 1,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,84</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,76</t>
+          <t>0,47; 1,73</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3820</t>
+          <t>0; 3759</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 5032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3468</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 3916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533; 4776</t>
+          <t>534; 4941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2653</t>
+          <t>0; 2663</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6300</t>
+          <t>0; 5836</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2631</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>711; 8732</t>
+          <t>684; 8255</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2461</t>
+          <t>0; 2187</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>670; 5945</t>
+          <t>719; 6270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2227</t>
+          <t>0; 2163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>620; 6085</t>
+          <t>634; 6121</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3755</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 4491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>0; 2990</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3756</t>
+          <t>0; 4127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4245</t>
+          <t>0; 4209</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>393; 4338</t>
+          <t>383; 4597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>0; 3149</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4700</t>
+          <t>0; 5096</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>621; 5502</t>
+          <t>622; 5587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>722; 7191</t>
+          <t>805; 7101</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 2562</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>0; 3543</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3916</t>
+          <t>0; 3140</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 3429</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2919</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3435</t>
+          <t>0; 3132</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3878,57 +3878,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1127; 7336</t>
+          <t>1128; 7279</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2657; 10494</t>
+          <t>2765; 11093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18; 6120</t>
+          <t>622; 6206</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 8558</t>
+          <t>0; 8563</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2505; 10386</t>
+          <t>2520; 10312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>619; 6144</t>
+          <t>612; 5975</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4279; 15396</t>
+          <t>4082; 15143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,27 +654,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,68</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,53</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,57</t>
+          <t>1,5; 16,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 11,49</t>
+          <t>0,97; 8,61</t>
         </is>
       </c>
     </row>
@@ -1074,29 +1074,29 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,64; 13,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,03</t>
+          <t>0,72; 6,5</t>
         </is>
       </c>
     </row>
@@ -1219,27 +1219,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>5,13%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,99</t>
+          <t>0,0; 10,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1494,29 +1494,29 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,91</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,46; 6,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,26</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,81</t>
+          <t>0,39; 3,92</t>
         </is>
       </c>
     </row>
@@ -1629,37 +1629,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,43</t>
+          <t>0,34; 1,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,73</t>
+          <t>0,42; 1,46</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2146,27 +2146,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>818</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4188</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3759</t>
+          <t>0; 4102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5032</t>
+          <t>0; 5887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3468</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3916</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2504,27 +2504,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2572,34 +2572,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2440</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2661</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>534; 4941</t>
+          <t>0; 3828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2663</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5836</t>
+          <t>475; 5179</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>0; 2670</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>684; 8255</t>
+          <t>652; 5772</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2770,29 +2770,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2381</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>719; 6270</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2242</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>743; 6145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2163</t>
+          <t>0; 1790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>634; 6121</t>
+          <t>717; 6464</t>
         </is>
       </c>
     </row>
@@ -2915,27 +2915,27 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2983,27 +2983,27 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3359</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4491</t>
+          <t>0; 3308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3726</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4127</t>
+          <t>0; 4069</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3326,37 +3326,37 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3394,29 +3394,29 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2474</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4209</t>
+          <t>0; 3523</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>383; 4597</t>
+          <t>0; 5288</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5096</t>
+          <t>347; 4697</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>622; 5587</t>
+          <t>624; 6124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>805; 7101</t>
+          <t>695; 7001</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,37 +3597,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3485</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2562</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3543</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3140</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3527</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3429</t>
+          <t>0; 3500</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2897</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3132</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,49 +3805,49 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>5452</t>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1128; 7279</t>
+          <t>616; 6517</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2765; 11093</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>622; 6206</t>
+          <t>1142; 7087</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 8563</t>
+          <t>2789; 10451</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2520; 10312</t>
+          <t>2413; 9915</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>612; 5975</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4082; 15143</t>
+          <t>3587; 12528</t>
         </is>
       </c>
     </row>
